--- a/Estimación de tareas/Tabla de Tareas V7 - Prescripciones Ortoprotesicas.xlsx
+++ b/Estimación de tareas/Tabla de Tareas V7 - Prescripciones Ortoprotesicas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClaudiaAlvarezDiaz\Documents\EJIE\Repo OSAKIDETZA\Osakidetza\Estimación de tareas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42916FB7-ACD3-476D-ADB6-54083C85E2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BD89B34-0857-4464-9AD3-A74C243A8B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45510" yWindow="210" windowWidth="2970" windowHeight="585" xr2:uid="{B85A3252-877B-4899-93D0-3BF0E3D23998}"/>
+    <workbookView xWindow="45510" yWindow="210" windowWidth="2970" windowHeight="585" xr2:uid="{BBB5C245-1F38-439C-9668-9321AE1263BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Tareas V7" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="500">
   <si>
     <t>#</t>
   </si>
@@ -139,291 +139,297 @@
     <t>Cambio de rol activo en sesión si el usuario tiene varios roles</t>
   </si>
   <si>
+    <t>Nueva. No existe en el Excel. Revisión Igor: según arquitecto, el usuario logueado tendrá X roles asignados y no debería haber cambio de rol en mitad de sesión. Valorar eliminación si se confirma que Osabide Global resuelve el contexto de roles al autenticarse (ver P-01). Se mantiene por precaución hasta respuesta del cliente</t>
+  </si>
+  <si>
+    <t>Lógica de cambio de rol activo: recarga de permisos y contexto</t>
+  </si>
+  <si>
+    <t>Nueva. No existe en el Excel. Revisión Igor: misma observación que #7. Si no aplica cambio de rol en sesión, esta tarea se eliminaría junto con #7 (-32h). Condicionada a P-01</t>
+  </si>
+  <si>
+    <t>Modo acceso</t>
+  </si>
+  <si>
+    <t>Modo con/sin paciente</t>
+  </si>
+  <si>
+    <t>Lógica para admitir acceso con paciente asociado (cita activa) y sin paciente (gestión propia del facultativo)</t>
+  </si>
+  <si>
+    <t>Nueva. El sistema debe diferenciar ambos modos y adaptar el listado de prescripciones en consecuencia</t>
+  </si>
+  <si>
+    <t>Adaptación de interfaz según modo de acceso (con paciente: preselecciona paciente; sin paciente: muestra todas las prescripciones del facultativo)</t>
+  </si>
+  <si>
+    <t>Nueva</t>
+  </si>
+  <si>
+    <t>CATÁLOGO</t>
+  </si>
+  <si>
+    <t>BBDD</t>
+  </si>
+  <si>
+    <t>Diseño BBDD</t>
+  </si>
+  <si>
+    <t>Diseño de base de datos del catálogo: campos del nomenclátor del Departamento + campos propios de Osakidetza</t>
+  </si>
+  <si>
+    <t>T-007</t>
+  </si>
+  <si>
+    <t>Creación y pruebas de base de datos del catálogo</t>
+  </si>
+  <si>
+    <t>T-008</t>
+  </si>
+  <si>
+    <t>Gobierno de edición</t>
+  </si>
+  <si>
+    <t>Definición y desarrollo de campos propios de Osakidetza (activo sí/no, favoritos por facultativo, campos de caracterización de producto, campos adicionales para reglas de indicación)</t>
+  </si>
+  <si>
+    <t>Nueva. Ampliada: incluye campos de caracterización de productos (decisión cliente 11/03/2026). Revisión Igor: opina que la definición de campos propios va incluida en T-007 (#11). Parcialmente cierto para campos simples (activo sí/no), pero la ampliación con campos de caracterización y reglas de indicación (decisión cliente 11/03) no estaba en el alcance original de T-007. Se mantiene como tarea separada por ese motivo; podría reducirse a ~32h si se absorbe la parte más básica en #11</t>
+  </si>
+  <si>
+    <t>Sincronización</t>
+  </si>
+  <si>
+    <t>Carga masiva por ficheros</t>
+  </si>
+  <si>
+    <t>Proceso de importación periódica de ficheros del nomenclátor del Departamento (~1.000 productos): lectura, parseo, validación de formato/contenido, carga en BBDD, gestión de errores (duplicados, campos faltantes, formatos incorrectos), log de auditoría de cada carga. NO se usa replicación BBDD (Golden Gate descartado por coste)</t>
+  </si>
+  <si>
+    <t>T-009</t>
+  </si>
+  <si>
+    <t>Actualizada: la carga es por importación de ficheros (CSV/XML/otro), no por sincronización genérica de BBDD</t>
+  </si>
+  <si>
+    <t>Carga bajo demanda por ficheros</t>
+  </si>
+  <si>
+    <t>Ejecución manual del mismo proceso de importación de ficheros fuera de ciclo. Incluye subida manual del fichero por parte del administrador</t>
+  </si>
+  <si>
+    <t>T-010</t>
+  </si>
+  <si>
+    <t>Actualizada: misma lógica de ficheros que #14 pero ejecución manual</t>
+  </si>
+  <si>
+    <t>Gestión de ficheros y failover</t>
+  </si>
+  <si>
+    <t>Mecanismo de recepción de ficheros del Departamento (SFTP, carpeta compartida o API de descarga), validación previa al procesamiento, gestión de reintentos si la importación falla, y garantía de disponibilidad 24x7 del catálogo local</t>
+  </si>
+  <si>
+    <t>Actualizada: pasa de réplica BBDD a gestión de ficheros + failover local</t>
+  </si>
+  <si>
+    <t>Gestión catálogo</t>
+  </si>
+  <si>
+    <t>Pantalla gestión</t>
+  </si>
+  <si>
+    <t>Pantalla de gestión/administración del catálogo: listado con filtros, ficha de producto editable (campos Osakidetza + campos de caracterización), activar/desactivar productos</t>
+  </si>
+  <si>
+    <t>T-011</t>
+  </si>
+  <si>
+    <t>Ampliada: incluye campos de caracterización de producto (decisión cliente 11/03/2026)</t>
+  </si>
+  <si>
+    <t>APIs catálogo</t>
+  </si>
+  <si>
+    <t>APIs CRUD de gestión del catálogo incluyendo campos de caracterización</t>
+  </si>
+  <si>
+    <t>T-012</t>
+  </si>
+  <si>
+    <t>Ampliada: incluye persistencia de caracterización</t>
+  </si>
+  <si>
+    <t>Búsqueda</t>
+  </si>
+  <si>
+    <t>Pantalla búsqueda</t>
+  </si>
+  <si>
+    <t>Pantalla/diálogo de búsqueda de catálogo de productos, con filtros y acceso al detalle</t>
+  </si>
+  <si>
+    <t>T-013</t>
+  </si>
+  <si>
+    <t>Filtro por tipo</t>
+  </si>
+  <si>
+    <t>Filtro de productos por tipo</t>
+  </si>
+  <si>
+    <t>T-014</t>
+  </si>
+  <si>
+    <t>Filtro por familia</t>
+  </si>
+  <si>
+    <t>Filtro de producto por familia (grupo &gt; subgrupo &gt; categoría)</t>
+  </si>
+  <si>
+    <t>T-015</t>
+  </si>
+  <si>
+    <t>Filtro por código</t>
+  </si>
+  <si>
+    <t>Filtro de producto por código</t>
+  </si>
+  <si>
+    <t>T-016</t>
+  </si>
+  <si>
+    <t>Filtro por descripción</t>
+  </si>
+  <si>
+    <t>Filtro de producto por descripción (texto libre)</t>
+  </si>
+  <si>
+    <t>Nueva. Los filtros del Excel no incluyen búsqueda por descripción</t>
+  </si>
+  <si>
+    <t>Selección</t>
+  </si>
+  <si>
+    <t>Pantalla selección</t>
+  </si>
+  <si>
+    <t>Pantalla de selección de productos dentro de la prescripción: favoritos primero + productos similares</t>
+  </si>
+  <si>
+    <t>T-017</t>
+  </si>
+  <si>
+    <t>Productos no disponibles</t>
+  </si>
+  <si>
+    <t>Mostrar todos los productos del catálogo, incluso los que el facultativo no puede prescribir (aparecen como no disponibles para que pueda solicitar permisos)</t>
+  </si>
+  <si>
+    <t>Nueva. RN-13: productos sin permiso visibles pero marcados como no disponibles</t>
+  </si>
+  <si>
+    <t>Validación back: marcar productos como no disponibles según permisos del facultativo</t>
+  </si>
+  <si>
+    <t>Nueva. Complemento back de #25</t>
+  </si>
+  <si>
+    <t>Favoritos</t>
+  </si>
+  <si>
+    <t>Pantalla favoritos</t>
+  </si>
+  <si>
+    <t>Pantalla de gestión de favoritos del facultativo</t>
+  </si>
+  <si>
+    <t>T-018</t>
+  </si>
+  <si>
+    <t>Sistema favoritos</t>
+  </si>
+  <si>
+    <t>Sistema de gestión de favoritos: almacenamiento en BBDD de Osakidetza, marcado por el facultativo desde la prescripción</t>
+  </si>
+  <si>
+    <t>T-019</t>
+  </si>
+  <si>
+    <t>PRESCRIPCIÓN</t>
+  </si>
+  <si>
+    <t>Diseño de base de datos de prescripciones (prescripción, materiales, estados, histórico, adjuntos)</t>
+  </si>
+  <si>
+    <t>T-020</t>
+  </si>
+  <si>
+    <t>Creación y pruebas de BD de prescripciones</t>
+  </si>
+  <si>
+    <t>T-021</t>
+  </si>
+  <si>
+    <t>Listado</t>
+  </si>
+  <si>
+    <t>Pantalla listado</t>
+  </si>
+  <si>
+    <t>Pantalla de consulta/listado de prescripciones con filtros (por paciente, por facultativo, por estado, por fecha, por OSI, por tipo producto)</t>
+  </si>
+  <si>
+    <t>T-022</t>
+  </si>
+  <si>
+    <t>APIs búsqueda</t>
+  </si>
+  <si>
+    <t>APIs de búsqueda/consulta de prescripciones con filtros</t>
+  </si>
+  <si>
+    <t>T-023</t>
+  </si>
+  <si>
+    <t>Indicador visual</t>
+  </si>
+  <si>
+    <t>Indicador visual de estado de dispensación en el listado (icono/color + columna de estado textual)</t>
+  </si>
+  <si>
+    <t>Nueva. Sin ella el prescriptor no identifica visualmente el estado</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>API detalle</t>
+  </si>
+  <si>
+    <t>API consulta detalles de una prescripción</t>
+  </si>
+  <si>
+    <t>T-024</t>
+  </si>
+  <si>
+    <t>Pantalla detalle</t>
+  </si>
+  <si>
+    <t>Pantalla de consulta de detalle de prescripción (modo lectura, datos completos, estado de cada material)</t>
+  </si>
+  <si>
+    <t>T-025</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Pantalla de histórico de la prescripción: acciones realizadas, cambios de estado, fechas</t>
+  </si>
+  <si>
     <t>Nueva. No existe en el Excel</t>
   </si>
   <si>
-    <t>Lógica de cambio de rol activo: recarga de permisos y contexto</t>
-  </si>
-  <si>
-    <t>Modo acceso</t>
-  </si>
-  <si>
-    <t>Modo con/sin paciente</t>
-  </si>
-  <si>
-    <t>Lógica para admitir acceso con paciente asociado (cita activa) y sin paciente (gestión propia del facultativo)</t>
-  </si>
-  <si>
-    <t>Nueva. El sistema debe diferenciar ambos modos y adaptar el listado de prescripciones en consecuencia</t>
-  </si>
-  <si>
-    <t>Adaptación de interfaz según modo de acceso (con paciente: preselecciona paciente; sin paciente: muestra todas las prescripciones del facultativo)</t>
-  </si>
-  <si>
-    <t>Nueva</t>
-  </si>
-  <si>
-    <t>CATÁLOGO</t>
-  </si>
-  <si>
-    <t>BBDD</t>
-  </si>
-  <si>
-    <t>Diseño BBDD</t>
-  </si>
-  <si>
-    <t>Diseño de base de datos del catálogo: campos del nomenclátor del Departamento + campos propios de Osakidetza</t>
-  </si>
-  <si>
-    <t>T-007</t>
-  </si>
-  <si>
-    <t>Creación y pruebas de base de datos del catálogo</t>
-  </si>
-  <si>
-    <t>T-008</t>
-  </si>
-  <si>
-    <t>Gobierno de edición</t>
-  </si>
-  <si>
-    <t>Definición y desarrollo de campos propios de Osakidetza (activo sí/no, favoritos por facultativo, campos de caracterización de producto, campos adicionales para reglas de indicación)</t>
-  </si>
-  <si>
-    <t>Nueva. Ampliada: incluye campos de caracterización de productos (decisión cliente 11/03/2026)</t>
-  </si>
-  <si>
-    <t>Sincronización</t>
-  </si>
-  <si>
-    <t>Carga masiva por ficheros</t>
-  </si>
-  <si>
-    <t>Proceso de importación periódica de ficheros del nomenclátor del Departamento (~1.000 productos): lectura, parseo, validación de formato/contenido, carga en BBDD, gestión de errores (duplicados, campos faltantes, formatos incorrectos), log de auditoría de cada carga. NO se usa replicación BBDD (Golden Gate descartado por coste)</t>
-  </si>
-  <si>
-    <t>T-009</t>
-  </si>
-  <si>
-    <t>Actualizada: la carga es por importación de ficheros (CSV/XML/otro), no por sincronización genérica de BBDD</t>
-  </si>
-  <si>
-    <t>Carga bajo demanda por ficheros</t>
-  </si>
-  <si>
-    <t>Ejecución manual del mismo proceso de importación de ficheros fuera de ciclo. Incluye subida manual del fichero por parte del administrador</t>
-  </si>
-  <si>
-    <t>T-010</t>
-  </si>
-  <si>
-    <t>Actualizada: misma lógica de ficheros que #14 pero ejecución manual</t>
-  </si>
-  <si>
-    <t>Gestión de ficheros y failover</t>
-  </si>
-  <si>
-    <t>Mecanismo de recepción de ficheros del Departamento (SFTP, carpeta compartida o API de descarga), validación previa al procesamiento, gestión de reintentos si la importación falla, y garantía de disponibilidad 24x7 del catálogo local</t>
-  </si>
-  <si>
-    <t>Actualizada: pasa de réplica BBDD a gestión de ficheros + failover local</t>
-  </si>
-  <si>
-    <t>Gestión catálogo</t>
-  </si>
-  <si>
-    <t>Pantalla gestión</t>
-  </si>
-  <si>
-    <t>Pantalla de gestión/administración del catálogo: listado con filtros, ficha de producto editable (campos Osakidetza + campos de caracterización), activar/desactivar productos</t>
-  </si>
-  <si>
-    <t>T-011</t>
-  </si>
-  <si>
-    <t>Ampliada: incluye campos de caracterización de producto (decisión cliente 11/03/2026)</t>
-  </si>
-  <si>
-    <t>APIs catálogo</t>
-  </si>
-  <si>
-    <t>APIs CRUD de gestión del catálogo incluyendo campos de caracterización</t>
-  </si>
-  <si>
-    <t>T-012</t>
-  </si>
-  <si>
-    <t>Ampliada: incluye persistencia de caracterización</t>
-  </si>
-  <si>
-    <t>Búsqueda</t>
-  </si>
-  <si>
-    <t>Pantalla búsqueda</t>
-  </si>
-  <si>
-    <t>Pantalla/diálogo de búsqueda de catálogo de productos, con filtros y acceso al detalle</t>
-  </si>
-  <si>
-    <t>T-013</t>
-  </si>
-  <si>
-    <t>Filtro por tipo</t>
-  </si>
-  <si>
-    <t>Filtro de productos por tipo</t>
-  </si>
-  <si>
-    <t>T-014</t>
-  </si>
-  <si>
-    <t>Filtro por familia</t>
-  </si>
-  <si>
-    <t>Filtro de producto por familia (grupo &gt; subgrupo &gt; categoría)</t>
-  </si>
-  <si>
-    <t>T-015</t>
-  </si>
-  <si>
-    <t>Filtro por código</t>
-  </si>
-  <si>
-    <t>Filtro de producto por código</t>
-  </si>
-  <si>
-    <t>T-016</t>
-  </si>
-  <si>
-    <t>Filtro por descripción</t>
-  </si>
-  <si>
-    <t>Filtro de producto por descripción (texto libre)</t>
-  </si>
-  <si>
-    <t>Nueva. Los filtros del Excel no incluyen búsqueda por descripción</t>
-  </si>
-  <si>
-    <t>Selección</t>
-  </si>
-  <si>
-    <t>Pantalla selección</t>
-  </si>
-  <si>
-    <t>Pantalla de selección de productos dentro de la prescripción: favoritos primero + productos similares</t>
-  </si>
-  <si>
-    <t>T-017</t>
-  </si>
-  <si>
-    <t>Productos no disponibles</t>
-  </si>
-  <si>
-    <t>Mostrar todos los productos del catálogo, incluso los que el facultativo no puede prescribir (aparecen como no disponibles para que pueda solicitar permisos)</t>
-  </si>
-  <si>
-    <t>Nueva. RN-13: productos sin permiso visibles pero marcados como no disponibles</t>
-  </si>
-  <si>
-    <t>Validación back: marcar productos como no disponibles según permisos del facultativo</t>
-  </si>
-  <si>
-    <t>Nueva. Complemento back de #25</t>
-  </si>
-  <si>
-    <t>Favoritos</t>
-  </si>
-  <si>
-    <t>Pantalla favoritos</t>
-  </si>
-  <si>
-    <t>Pantalla de gestión de favoritos del facultativo</t>
-  </si>
-  <si>
-    <t>T-018</t>
-  </si>
-  <si>
-    <t>Sistema favoritos</t>
-  </si>
-  <si>
-    <t>Sistema de gestión de favoritos: almacenamiento en BBDD de Osakidetza, marcado por el facultativo desde la prescripción</t>
-  </si>
-  <si>
-    <t>T-019</t>
-  </si>
-  <si>
-    <t>PRESCRIPCIÓN</t>
-  </si>
-  <si>
-    <t>Diseño de base de datos de prescripciones (prescripción, materiales, estados, histórico, adjuntos)</t>
-  </si>
-  <si>
-    <t>T-020</t>
-  </si>
-  <si>
-    <t>Creación y pruebas de BD de prescripciones</t>
-  </si>
-  <si>
-    <t>T-021</t>
-  </si>
-  <si>
-    <t>Listado</t>
-  </si>
-  <si>
-    <t>Pantalla listado</t>
-  </si>
-  <si>
-    <t>Pantalla de consulta/listado de prescripciones con filtros (por paciente, por facultativo, por estado, por fecha, por OSI, por tipo producto)</t>
-  </si>
-  <si>
-    <t>T-022</t>
-  </si>
-  <si>
-    <t>APIs búsqueda</t>
-  </si>
-  <si>
-    <t>APIs de búsqueda/consulta de prescripciones con filtros</t>
-  </si>
-  <si>
-    <t>T-023</t>
-  </si>
-  <si>
-    <t>Indicador visual</t>
-  </si>
-  <si>
-    <t>Indicador visual de estado de dispensación en el listado (icono/color + columna de estado textual)</t>
-  </si>
-  <si>
-    <t>Nueva. Sin ella el prescriptor no identifica visualmente el estado</t>
-  </si>
-  <si>
-    <t>Detalle</t>
-  </si>
-  <si>
-    <t>API detalle</t>
-  </si>
-  <si>
-    <t>API consulta detalles de una prescripción</t>
-  </si>
-  <si>
-    <t>T-024</t>
-  </si>
-  <si>
-    <t>Pantalla detalle</t>
-  </si>
-  <si>
-    <t>Pantalla de consulta de detalle de prescripción (modo lectura, datos completos, estado de cada material)</t>
-  </si>
-  <si>
-    <t>T-025</t>
-  </si>
-  <si>
-    <t>Histórico</t>
-  </si>
-  <si>
-    <t>Pantalla de histórico de la prescripción: acciones realizadas, cambios de estado, fechas</t>
-  </si>
-  <si>
     <t>API/servicio de histórico/auditoría de la prescripción</t>
   </si>
   <si>
@@ -748,16 +754,19 @@
     <t>Estados prescripción</t>
   </si>
   <si>
-    <t>Implementación de la máquina de estados de la prescripción (8 estados, transiciones definidas en §3.4)</t>
-  </si>
-  <si>
-    <t>Nueva. Crítica. No existe como tarea independiente en el Excel</t>
+    <t>Implementación de la lógica de transiciones de estado de la prescripción (8 estados, transiciones definidas en §3.4). No requiere framework formal de state machine; se trata de codificar las transiciones permitidas, validaciones de cambio de estado y eventos asociados como lógica de negocio</t>
+  </si>
+  <si>
+    <t>Nueva. Crítica. No existe como tarea independiente en el Excel. Revisión Igor: desaconseja usar un patrón de máquina de estados formal y sugiere manejar estados sin ese patrón. De acuerdo: no se propone un framework (Spring Statemachine o similar), sino la implementación de las reglas de transición como lógica de negocio. La tarea sigue siendo necesaria porque los 8 estados con sus transiciones deben codificarse y testearse independientemente de cómo se implementen</t>
   </si>
   <si>
     <t>Estados material</t>
   </si>
   <si>
-    <t>Implementación de la máquina de estados del material (10 estados, transiciones definidas en §3.5)</t>
+    <t>Implementación de la lógica de transiciones de estado del material (10 estados, transiciones definidas en §3.5). No requiere framework formal de state machine; misma aproximación que #70 aplicada a los estados del material</t>
+  </si>
+  <si>
+    <t>Nueva. Crítica. No existe como tarea independiente en el Excel. Revisión Igor: misma observación que #70. Se clarifica que no implica framework de máquina de estados</t>
   </si>
   <si>
     <t>Caducidad</t>
@@ -805,7 +814,7 @@
     <t>T-051</t>
   </si>
   <si>
-    <t>Revisar: el Excel dice "Bloquear prescripción" pero el enfoque es por material, no por prescripción</t>
+    <t>Revisar: el Excel dice "Bloquear prescripción" pero el enfoque es por material, no por prescripción. Revisión Igor: indica que el requerimiento original era bloquear la prescripción completa, no por material. Discrepancia crítica: si la dispensación es parcial (material a material), el bloqueo debería ser por material; si es por prescripción completa, cambia la arquitectura de dispensación. Requiere resolución urgente — ver P-11</t>
   </si>
   <si>
     <t>Desbloquear material</t>
@@ -838,7 +847,7 @@
     <t>Enviar solicitud de visado al Departamento al firmar prescripción con material que requiere visado</t>
   </si>
   <si>
-    <t>Nueva. T-054 mezcla envío y recepción; deberían ser 2 tareas separadas</t>
+    <t>Nueva. T-054 mezcla envío y recepción; deberían ser 2 tareas separadas. Revisión Igor: indica que actualmente NO existe canal electrónico para enviar la solicitud al Departamento; el proceso es con papel que el propio paciente lleva. Si se confirma, esta tarea debería transformarse en "generar documento de solicitud de visado para impresión" (podría absorberse en #66, generación de PDF). Requiere resolución — ver P-12</t>
   </si>
   <si>
     <t>Recibir estado visado</t>
@@ -862,9 +871,15 @@
     <t>Pantalla/acción para que el prescriptor valide o rechace un material dispensado que requiere validación clínica</t>
   </si>
   <si>
+    <t>Nueva. Derivada del modelo de estados del material (§3.5). Revisión Igor: cuestiona si es requerimiento nuevo. Es funcionalidad derivada de la lógica de estados (no invención), pero es un flujo secundario. Prioridad F5 (no critical path); si al llegar a esa fase el cliente no la necesita, se puede eliminar sin impacto</t>
+  </si>
+  <si>
     <t>Lógica back de validación post-dispensación: cambiar estado material según decisión del prescriptor</t>
   </si>
   <si>
+    <t>Nueva. Derivada del modelo de estados del material. Revisión Igor: misma observación que #80. Prioridad F5; eliminable si el cliente no la necesita</t>
+  </si>
+  <si>
     <t>Dispensación parcial</t>
   </si>
   <si>
@@ -913,6 +928,9 @@
     <t>Crear tarea pendiente cuando un material dispensado requiere validación del prescriptor</t>
   </si>
   <si>
+    <t>Nueva. Derivada del flujo de validación post-dispensación (#80/#81). Revisión Igor: misma observación — vinculada a #80/#81. Si la validación post-dispensación no se implementa, esta tarea también se elimina. Prioridad F5</t>
+  </si>
+  <si>
     <t>Tarea dispensación</t>
   </si>
   <si>
@@ -961,12 +979,18 @@
     <t>Pantalla de gestión de establecimientos (listado, alta, edición, baja)</t>
   </si>
   <si>
+    <t>Nueva. Revisión Igor: cuestiona si la gestión de establecimientos (ortopedias) es competencia de Osakidetza o del Departamento. Si el catálogo de establecimientos lo mantiene el Departamento y llega como dato maestro (similar al nomenclátor), Osakidetza no necesita CRUD propio y esta tarea se eliminaría. Requiere resolución — ver P-13</t>
+  </si>
+  <si>
     <t>APIs establecimientos</t>
   </si>
   <si>
     <t>APIs CRUD de gestión de establecimientos</t>
   </si>
   <si>
+    <t>Nueva. Revisión Igor: misma observación que #92. Condicionada a P-13</t>
+  </si>
+  <si>
     <t>Configuraciones</t>
   </si>
   <si>
@@ -988,7 +1012,7 @@
     <t>T-003</t>
   </si>
   <si>
-    <t>Revisar: T-003 mezcla configuraciones + roles en una sola tarea; valorar separar</t>
+    <t>T-003 cubre configuraciones del sistema (no incluye roles, que van en #5/#6). Revisión Igor: confirma que T-003 siempre fue solo configuraciones, no roles</t>
   </si>
   <si>
     <t>TRANSVERSAL</t>
@@ -1027,7 +1051,7 @@
     <t>Modificar el proceso de unificación de pacientes existente en Osakidetza para incluir prescripciones ortoprotésicas</t>
   </si>
   <si>
-    <t>Nueva. Solo aparece mencionada fuera de la tabla principal del Excel</t>
+    <t>Nueva. Revisión Igor: indica que se decidió no tocar este proceso por ahora, ya que requiere cambiar el proceso globalmente para Departamento, Osakidetza y establecimientos. Si se confirma, esta tarea se eliminaría del alcance (-24h) y quedaría como requisito futuro. Requiere resolución — ver P-14</t>
   </si>
   <si>
     <t>Módulo SOA</t>
@@ -1450,7 +1474,7 @@
     <t>F0-F6</t>
   </si>
   <si>
-    <t>Arquitectura, BBDD, maquina de estados</t>
+    <t>Arquitectura, BBDD, logica de estados</t>
   </si>
   <si>
     <t>Backend Dev 1</t>
@@ -2071,7 +2095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C72080-F96A-4662-B897-F13046C62F8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCFCF80C-979E-4ECB-BA05-7ECDB1A033C5}">
   <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2082,7 +2106,7 @@
     <col min="5" max="5" width="80.6328125" style="29" customWidth="1"/>
     <col min="6" max="7" width="12.6328125" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" customWidth="1"/>
-    <col min="9" max="9" width="60.6328125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="80.6328125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2224,7 +2248,7 @@
       </c>
       <c r="I5" s="20"/>
     </row>
-    <row r="6" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2282,7 +2306,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2311,7 +2335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2337,10 +2361,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2348,13 +2372,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>16</v>
@@ -2366,7 +2390,7 @@
         <v>24</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -2377,13 +2401,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>13</v>
@@ -2395,7 +2419,7 @@
         <v>16</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -2403,22 +2427,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H12" s="5">
         <v>40</v>
@@ -2430,43 +2454,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" s="5">
         <v>32</v>
       </c>
       <c r="I13" s="21"/>
     </row>
-    <row r="14" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>16</v>
@@ -2478,7 +2502,7 @@
         <v>48</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="52.5" x14ac:dyDescent="0.35">
@@ -2486,28 +2510,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H15" s="5">
         <v>60</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -2515,28 +2539,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H16" s="5">
         <v>16</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
@@ -2544,16 +2568,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>16</v>
@@ -2565,7 +2589,7 @@
         <v>40</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -2573,28 +2597,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H18" s="5">
         <v>48</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -2602,28 +2626,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" s="5">
         <v>40</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -2631,22 +2655,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H20" s="5">
         <v>32</v>
@@ -2658,22 +2682,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="5">
         <v>8</v>
@@ -2685,22 +2709,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" s="5">
         <v>16</v>
@@ -2712,22 +2736,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="5">
         <v>8</v>
@@ -2739,16 +2763,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>16</v>
@@ -2760,7 +2784,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -2768,22 +2792,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" s="5">
         <v>40</v>
@@ -2795,16 +2819,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>13</v>
@@ -2816,7 +2840,7 @@
         <v>16</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -2824,16 +2848,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>16</v>
@@ -2845,7 +2869,7 @@
         <v>16</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -2853,22 +2877,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="5">
         <v>24</v>
@@ -2880,22 +2904,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="5">
         <v>16</v>
@@ -2907,22 +2931,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H30" s="7">
         <v>48</v>
@@ -2934,22 +2958,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H31" s="7">
         <v>32</v>
@@ -2961,22 +2985,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" s="7">
         <v>48</v>
@@ -2988,22 +3012,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="7">
         <v>40</v>
@@ -3015,16 +3039,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>13</v>
@@ -3036,7 +3060,7 @@
         <v>8</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -3044,22 +3068,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H35" s="7">
         <v>24</v>
@@ -3071,22 +3095,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H36" s="7">
         <v>40</v>
@@ -3098,16 +3122,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>13</v>
@@ -3119,7 +3143,7 @@
         <v>24</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -3127,16 +3151,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>16</v>
@@ -3148,7 +3172,7 @@
         <v>24</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -3156,16 +3180,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>13</v>
@@ -3177,7 +3201,7 @@
         <v>16</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -3185,22 +3209,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H40" s="7">
         <v>60</v>
@@ -3212,28 +3236,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H41" s="7">
         <v>40</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -3241,28 +3265,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H42" s="7">
         <v>40</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -3270,22 +3294,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H43" s="7">
         <v>24</v>
@@ -3297,55 +3321,55 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H44" s="7">
         <v>16</v>
       </c>
       <c r="I44" s="22"/>
     </row>
-    <row r="45" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H45" s="7">
         <v>16</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -3353,16 +3377,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>13</v>
@@ -3374,7 +3398,7 @@
         <v>20</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -3382,16 +3406,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>16</v>
@@ -3403,7 +3427,7 @@
         <v>24</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -3411,16 +3435,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>13</v>
@@ -3432,7 +3456,7 @@
         <v>32</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -3440,16 +3464,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>13</v>
@@ -3461,7 +3485,7 @@
         <v>8</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -3469,28 +3493,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H50" s="7">
         <v>24</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -3498,28 +3522,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H51" s="7">
         <v>40</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -3527,22 +3551,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H52" s="7">
         <v>40</v>
@@ -3554,22 +3578,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H53" s="7">
         <v>32</v>
@@ -3581,22 +3605,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H54" s="7">
         <v>16</v>
@@ -3608,16 +3632,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>13</v>
@@ -3629,7 +3653,7 @@
         <v>8</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -3637,22 +3661,22 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H56" s="7">
         <v>32</v>
@@ -3664,16 +3688,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>13</v>
@@ -3685,7 +3709,7 @@
         <v>8</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -3693,22 +3717,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H58" s="7">
         <v>20</v>
@@ -3720,16 +3744,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>13</v>
@@ -3741,7 +3765,7 @@
         <v>8</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -3749,22 +3773,22 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H60" s="7">
         <v>32</v>
@@ -3776,16 +3800,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>13</v>
@@ -3797,7 +3821,7 @@
         <v>16</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -3805,22 +3829,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H62" s="7">
         <v>40</v>
@@ -3832,16 +3856,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>16</v>
@@ -3853,7 +3877,7 @@
         <v>20</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -3861,16 +3885,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>16</v>
@@ -3882,7 +3906,7 @@
         <v>16</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -3890,16 +3914,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>16</v>
@@ -3911,7 +3935,7 @@
         <v>8</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -3919,22 +3943,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H66" s="7">
         <v>12</v>
@@ -3946,22 +3970,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H67" s="7">
         <v>40</v>
@@ -3973,22 +3997,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H68" s="7">
         <v>16</v>
@@ -4000,72 +4024,72 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H69" s="7">
         <v>24</v>
       </c>
       <c r="I69" s="22"/>
     </row>
-    <row r="70" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H70" s="7">
         <v>24</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>16</v>
@@ -4077,24 +4101,24 @@
         <v>48</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>16</v>
@@ -4106,7 +4130,7 @@
         <v>48</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -4114,16 +4138,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>16</v>
@@ -4135,7 +4159,7 @@
         <v>20</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -4143,16 +4167,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>16</v>
@@ -4164,7 +4188,7 @@
         <v>12</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -4172,55 +4196,55 @@
         <v>74</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H75" s="9">
         <v>32</v>
       </c>
       <c r="I75" s="23"/>
     </row>
-    <row r="76" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A76" s="9">
         <v>75</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H76" s="9">
         <v>24</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
@@ -4228,28 +4252,28 @@
         <v>76</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H77" s="9">
         <v>16</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -4257,43 +4281,43 @@
         <v>77</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H78" s="9">
         <v>40</v>
       </c>
       <c r="I78" s="23"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>78</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>16</v>
@@ -4305,7 +4329,7 @@
         <v>24</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -4313,45 +4337,45 @@
         <v>79</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H80" s="9">
         <v>40</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A81" s="9">
         <v>80</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>13</v>
@@ -4363,24 +4387,24 @@
         <v>16</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A82" s="9">
         <v>81</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>16</v>
@@ -4392,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>32</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
@@ -4400,16 +4424,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>13</v>
@@ -4421,7 +4445,7 @@
         <v>16</v>
       </c>
       <c r="I83" s="23" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -4429,16 +4453,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>16</v>
@@ -4450,7 +4474,7 @@
         <v>24</v>
       </c>
       <c r="I84" s="23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
@@ -4458,22 +4482,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E85" s="24" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H85" s="11">
         <v>16</v>
@@ -4485,43 +4509,43 @@
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H86" s="11">
         <v>16</v>
       </c>
       <c r="I86" s="24"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A87" s="11">
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E87" s="24" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>16</v>
@@ -4533,7 +4557,7 @@
         <v>16</v>
       </c>
       <c r="I87" s="24" t="s">
-        <v>32</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
@@ -4541,16 +4565,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>16</v>
@@ -4562,7 +4586,7 @@
         <v>12</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -4570,22 +4594,22 @@
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E89" s="24" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H89" s="11">
         <v>40</v>
@@ -4597,22 +4621,22 @@
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H90" s="11">
         <v>32</v>
@@ -4624,16 +4648,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E91" s="24" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>13</v>
@@ -4645,7 +4669,7 @@
         <v>24</v>
       </c>
       <c r="I91" s="24" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
@@ -4653,16 +4677,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>16</v>
@@ -4674,24 +4698,24 @@
         <v>20</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A93" s="13">
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F93" s="13" t="s">
         <v>13</v>
@@ -4703,7 +4727,7 @@
         <v>24</v>
       </c>
       <c r="I93" s="25" t="s">
-        <v>32</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
@@ -4711,16 +4735,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F94" s="13" t="s">
         <v>16</v>
@@ -4732,7 +4756,7 @@
         <v>16</v>
       </c>
       <c r="I94" s="25" t="s">
-        <v>32</v>
+        <v>315</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
@@ -4740,16 +4764,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>13</v>
@@ -4761,36 +4785,36 @@
         <v>24</v>
       </c>
       <c r="I95" s="25" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A96" s="13">
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F96" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="H96" s="13">
         <v>24</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
@@ -4798,28 +4822,28 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F97" s="15" t="s">
         <v>13</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="H97" s="15">
         <v>48</v>
       </c>
       <c r="I97" s="26" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
@@ -4827,45 +4851,45 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F98" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H98" s="15">
         <v>40</v>
       </c>
       <c r="I98" s="26" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A99" s="15">
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F99" s="15" t="s">
         <v>16</v>
@@ -4877,7 +4901,7 @@
         <v>24</v>
       </c>
       <c r="I99" s="26" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -4885,55 +4909,55 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F100" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="H100" s="15">
         <v>40</v>
       </c>
       <c r="I100" s="26"/>
     </row>
-    <row r="101" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="15">
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F101" s="15" t="s">
         <v>13</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="H101" s="15">
         <v>120</v>
       </c>
       <c r="I101" s="26" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
@@ -4941,57 +4965,57 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="E102" s="26" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F102" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H102" s="15">
         <v>120</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="16">
         <v>102</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F103" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="H103" s="16">
         <v>0</v>
       </c>
       <c r="I103" s="27" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
@@ -4999,16 +5023,16 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="F104" s="13" t="s">
         <v>16</v>
@@ -5020,7 +5044,7 @@
         <v>48</v>
       </c>
       <c r="I104" s="25" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -5028,16 +5052,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F105" s="13" t="s">
         <v>13</v>
@@ -5049,7 +5073,7 @@
         <v>48</v>
       </c>
       <c r="I105" s="25" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
@@ -5057,16 +5081,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F106" s="13" t="s">
         <v>16</v>
@@ -5078,7 +5102,7 @@
         <v>32</v>
       </c>
       <c r="I106" s="25" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
@@ -5086,16 +5110,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F107" s="13" t="s">
         <v>16</v>
@@ -5107,7 +5131,7 @@
         <v>48</v>
       </c>
       <c r="I107" s="25" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -5115,16 +5139,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E108" s="22" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>13</v>
@@ -5136,7 +5160,7 @@
         <v>24</v>
       </c>
       <c r="I108" s="22" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
@@ -5144,16 +5168,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E109" s="21" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>13</v>
@@ -5165,7 +5189,7 @@
         <v>24</v>
       </c>
       <c r="I109" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="16" x14ac:dyDescent="0.4">
@@ -5174,7 +5198,7 @@
       <c r="C110" s="18"/>
       <c r="D110" s="18"/>
       <c r="E110" s="28" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F110" s="18"/>
       <c r="G110" s="18"/>
@@ -5185,13 +5209,13 @@
       <c r="I110" s="28"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I109" xr:uid="{15C72080-F96A-4662-B897-F13046C62F8B}"/>
+  <autoFilter ref="A1:I109" xr:uid="{CCFCF80C-979E-4ECB-BA05-7ECDB1A033C5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010E982F-DA6F-4B25-BB30-953D78F6DA9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C39B97B-E310-4E47-8F5A-2FDEDF1D94C7}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5205,24 +5229,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="31" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C2" s="31">
         <v>136</v>
@@ -5236,10 +5260,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="31" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C3" s="31">
         <v>184</v>
@@ -5253,10 +5277,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C4" s="31">
         <v>432</v>
@@ -5270,10 +5294,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="31" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C5" s="31">
         <v>32</v>
@@ -5287,10 +5311,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="31" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C6" s="31">
         <v>64</v>
@@ -5304,10 +5328,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C7" s="31">
         <v>96</v>
@@ -5321,10 +5345,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="31" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C8" s="31">
         <v>168</v>
@@ -5338,10 +5362,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="30" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C9" s="30">
         <v>1112</v>
@@ -5355,26 +5379,26 @@
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="17" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="31" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B14" s="31">
         <v>1630</v>
@@ -5383,12 +5407,12 @@
         <v>1972</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="31" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B15" s="31">
         <v>650</v>
@@ -5397,12 +5421,12 @@
         <v>1112</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B16" s="32">
         <v>2280</v>
@@ -5411,7 +5435,7 @@
         <v>3084</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -5420,223 +5444,224 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07AC1A57-3AEF-4B67-870B-84AE7A99AF86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D947AF43-4400-49D0-9CE0-4321EAFED533}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.6328125" customWidth="1"/>
-    <col min="2" max="2" width="35.6328125" customWidth="1"/>
-    <col min="3" max="4" width="16.6328125" customWidth="1"/>
-    <col min="5" max="5" width="50.6328125" customWidth="1"/>
+    <col min="2" max="2" width="40.6328125" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" customWidth="1"/>
+    <col min="4" max="4" width="16.6328125" customWidth="1"/>
+    <col min="5" max="5" width="55.6328125" customWidth="1"/>
     <col min="6" max="6" width="45.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="33" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="34" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>429</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="32"/>
       <c r="B12" s="32" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="32" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="35"/>
       <c r="B13" s="35" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="35"/>
@@ -5644,194 +5669,194 @@
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="17" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="30" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="31" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C18" s="36">
         <v>1</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="31" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="31" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="31" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C21" s="36">
         <v>1</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="31" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C22" s="36">
         <v>1</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="31" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C23" s="36">
         <v>1</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="31" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C24" s="36">
         <v>1</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="31" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C25" s="36">
         <v>1</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="31" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C26" s="36">
         <v>0.6</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="31" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C27" s="36">
         <v>1</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
